--- a/EmpManagement/defaults/Bulkupload_Demo_Sheet.xlsx
+++ b/EmpManagement/defaults/Bulkupload_Demo_Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeo\Desktop\project\zeo-hrms\EmpManagement\defaults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0819B10-78E3-40A0-9F52-985C150CAE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6739ED4F-4AE7-4A41-B87D-0241CB5F6430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{86F4AE16-A1C4-464D-9E72-7B30776A4DF7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{86F4AE16-A1C4-464D-9E72-7B30776A4DF7}"/>
   </bookViews>
   <sheets>
     <sheet name="EmployeeMaster" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Employee First Name</t>
   </si>
@@ -128,13 +128,16 @@
     <t>Employee Category Code</t>
   </si>
   <si>
-    <t>Field Name</t>
-  </si>
-  <si>
-    <t>Field Value</t>
-  </si>
-  <si>
     <t>Employee Company Email ID</t>
+  </si>
+  <si>
+    <t>Employee Profile Picture</t>
+  </si>
+  <si>
+    <t>Person ID</t>
+  </si>
+  <si>
+    <t>Employee Visa Location</t>
   </si>
 </sst>
 </file>
@@ -218,15 +221,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>38101</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>158749</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>25399</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -241,8 +244,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609601" y="390525"/>
-          <a:ext cx="9791700" cy="6134100"/>
+          <a:off x="609600" y="377824"/>
+          <a:ext cx="9912349" cy="6645275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -324,7 +327,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Employee Code                       :  </a:t>
+            <a:t>Employee Code 	-	</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="1200"/>
@@ -333,9 +336,13 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Employee First Name             :  </a:t>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Employee First Name 	-	</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="1200"/>
@@ -344,9 +351,122 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Employee Last Name             </a:t>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Employee Last Name	- 	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>The last name of the employee.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Personal Email ID                      -</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0" baseline="0"/>
+            <a:t>  	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>A valid email address. Duplicate values are not allowed.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Gender                                        - 	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>Allowed values are Male, Female, or Other.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>DOB(DD/MM/YYYY)   	 -	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>The date of birth in the format DD/MM/YYYY.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Joining Date(DD/MM/YYYY) 	-	 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>The joining date in the format DD/MM/YYYY.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Employee Branch ID                 -	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>The branch ID where the employee is posted.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Employee Department ID        -	 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>The department ID to which the employee belongs.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Employee Designation ID      </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="1200" b="0" baseline="0"/>
@@ -354,112 +474,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>:  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>The last name of the employee.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Personal Email ID                   </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>:</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>A valid email address. Duplicate values are not allowed.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Gender                                      :  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>Allowed values are Male, Female, or Other.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>DOB(DD/MM/YYYY)             </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t> :  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>The date of birth in the format DD/MM/YYYY.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Joining Date(DD/MM/YYYY)  :  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>The joining date in the format DD/MM/YYYY.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Employee Branch ID                :  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>The branch ID where the employee is posted.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Employee Department ID       :  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>The department ID to which the employee belongs.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Employee Designation ID      </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t> :  </a:t>
+            <a:t> - 	</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="1200"/>
@@ -468,13 +483,17 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Marital Status                           </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>:  Only Married, Single, Divorced, or Widow are allowed</a:t>
+          <a:endParaRPr lang="en-IN" sz="1200"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200" b="0"/>
+            <a:t>Marital Status                           -</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1200"/>
+            <a:t>	Only Married, Single, Divorced, or Widow are allowed</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -523,16 +542,6 @@
           <a:r>
             <a:rPr lang="en-IN" sz="1200"/>
             <a:t>: The name of the custom field. Must already exist in the database.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200" b="0"/>
-            <a:t>Field Value             </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-IN" sz="1200"/>
-            <a:t>: The value for the custom field</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -881,18 +890,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E35F595-30D5-4537-B8EA-5F50211BC1BF}">
-  <dimension ref="A1:AE1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="25.7109375" customWidth="1"/>
-    <col min="19" max="34" width="20.7109375" customWidth="1"/>
+    <col min="1" max="4" width="15.7265625" customWidth="1"/>
+    <col min="5" max="7" width="20.7265625" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" customWidth="1"/>
+    <col min="9" max="17" width="20.7265625" customWidth="1"/>
+    <col min="18" max="18" width="25.7265625" customWidth="1"/>
+    <col min="19" max="30" width="20.7265625" customWidth="1"/>
+    <col min="31" max="31" width="23" customWidth="1"/>
+    <col min="32" max="33" width="20.7265625" customWidth="1"/>
+    <col min="34" max="34" width="23.90625" customWidth="1"/>
+    <col min="35" max="35" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -912,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -985,6 +998,18 @@
       </c>
       <c r="AE1" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -996,21 +1021,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D2309B-D161-48CB-8165-FEFB40176371}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="26.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
-  </cols>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="26.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" s="2" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1038,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15F229-565E-427E-885F-2192367EC373}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
